--- a/webroot/export/customexcel/default_templates/profile_template_default.xlsx
+++ b/webroot/export/customexcel/default_templates/profile_template_default.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="388">
   <si>
     <t xml:space="preserve">${"image":{"displayValue":"Institutions.logo_content","imageWidth":"100","imageMarginLeft":"20","imageMarginTop":"5"}}</t>
   </si>
@@ -1176,10 +1176,7 @@
     <t xml:space="preserve">Student Date of Birth</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom Value</t>
+    <t xml:space="preserve">${"repeatColumns":{"displayValue":"StudentCustomFieldName.name"}}</t>
   </si>
   <si>
     <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.first_name","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
@@ -1194,7 +1191,7 @@
     <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.date_of_birth","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
   </si>
   <si>
-    <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.custom_field_name","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
+    <t xml:space="preserve">${"match": {"displayValue": "StudentCustomFieldValue.custom_field_value","type":"string","rows": {"matchFrom": "StudentCustomFieldValue.student_id","matchTo": "StudentDetailWithCustomField.student_id"},"columns": {"matchFrom": "StudentCustomFieldName.id","matchTo": "StudentCustomFieldValue.student_custom_field_id"}}}</t>
   </si>
   <si>
     <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.custom_field_value","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
@@ -1208,7 +1205,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1309,19 +1306,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1441,7 +1425,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1702,19 +1686,15 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1796,7 +1776,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IV1051"/>
-  <sheetFormatPr defaultColWidth="16.41796875" defaultRowHeight="16" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.43359375" defaultRowHeight="16" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="63.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="54.33"/>
@@ -22558,7 +22538,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.7421875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.02"/>
@@ -22599,9 +22579,7 @@
       <c r="E2" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="F2" s="66" t="s">
-        <v>382</v>
-      </c>
+      <c r="F2" s="66"/>
       <c r="G2" s="59"/>
       <c r="H2" s="59"/>
       <c r="I2" s="59"/>
@@ -22611,22 +22589,22 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>383</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C3" s="0" t="s">
         <v>384</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="D3" s="0" t="s">
         <v>385</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="E3" s="65" t="s">
         <v>386</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="F3" s="67" t="s">
         <v>387</v>
-      </c>
-      <c r="F3" s="68" t="s">
-        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -22649,7 +22627,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="16.41796875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.43359375" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="1" style="0" width="26.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.64"/>
@@ -22711,7 +22689,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="16.41796875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.43359375" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="1" style="0" width="24.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.64"/>
@@ -22771,7 +22749,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="16.41796875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.43359375" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="1" style="0" width="22.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.64"/>
@@ -22831,7 +22809,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="16.41796875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.43359375" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="1" style="0" width="22.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.64"/>
@@ -22891,7 +22869,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="16.41796875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.43359375" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="1" style="0" width="22.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.64"/>
@@ -22951,7 +22929,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="16.41796875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.43359375" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="1" style="0" width="22.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.64"/>
@@ -23011,7 +22989,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:X357"/>
-  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.5"/>
@@ -23672,7 +23650,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.65234375" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>

--- a/webroot/export/customexcel/default_templates/profile_template_default.xlsx
+++ b/webroot/export/customexcel/default_templates/profile_template_default.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="387">
   <si>
     <t xml:space="preserve">${"image":{"displayValue":"Institutions.logo_content","imageWidth":"100","imageMarginLeft":"20","imageMarginTop":"5"}}</t>
   </si>
@@ -1179,22 +1179,19 @@
     <t xml:space="preserve">${"repeatColumns":{"displayValue":"StudentCustomFieldName.name"}}</t>
   </si>
   <si>
-    <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.first_name","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.last_name","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.student_address","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.date_of_birth","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${"match": {"displayValue": "StudentCustomFieldValue.custom_field_value","type":"string","rows": {"matchFrom": "StudentCustomFieldValue.student_id","matchTo": "StudentDetailWithCustomField.student_id"},"columns": {"matchFrom": "StudentCustomFieldName.id","matchTo": "StudentCustomFieldValue.student_custom_field_id"}}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${"match": {"displayValue": "StudentDetailWithCustomField.custom_field_value","rows": {"matchFrom": "StudentDetailWithCustomField.id","matchTo": "StudentDetailWithCustomField.id"}}}</t>
+    <t xml:space="preserve">${"match": {"displayValue": "GeneralStudentDetails.first_name","rows": {"matchFrom": "GeneralStudentDetails.id","matchTo": "GeneralStudentDetails.id"}}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${"match": {"displayValue": "GeneralStudentDetails.last_name","rows": {"matchFrom": "GeneralStudentDetails.id","matchTo": "GeneralStudentDetails.id"}}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${"match": {"displayValue": "GeneralStudentDetails.student_address","rows": {"matchFrom": "GeneralStudentDetails.id","matchTo": "GeneralStudentDetails.id"}}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${"match": {"displayValue": "GeneralStudentDetails.date_of_birth","rows": {"matchFrom": "GeneralStudentDetails.id","matchTo": "GeneralStudentDetails.id"}}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${"match": {"displayValue": "StudentCustomFieldValueAnswer.name","type":"string","rows": {"matchFrom": "GeneralStudentDetails.student_id","matchTo": "StudentCustomFieldValueAnswer.student_id"},"columns": {"matchFrom": "StudentCustomFieldName.id","matchTo": "StudentCustomFieldValueAnswer.student_custom_field_id"}}}</t>
   </si>
 </sst>
 </file>
@@ -22603,9 +22600,7 @@
       <c r="E3" s="65" t="s">
         <v>386</v>
       </c>
-      <c r="F3" s="67" t="s">
-        <v>387</v>
-      </c>
+      <c r="F3" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="1">
